--- a/docs/TZ-Xipher-Desktop-v2.xlsx
+++ b/docs/TZ-Xipher-Desktop-v2.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C23"/>
+  <dimension ref="C2:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,6 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
           <t>XIPHER DESKTOP 2.0 — ТЕХНИЧЕСКОЕ ЗАДАНИЕ</t>
@@ -566,19 +565,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Полный паритет с TG Desktop + Discord-фичи. Версия ТЗ 2.0 от 03.10.2026</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
     <row r="5">
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>База для проверки: репозиторий после ночной смены (коммиты 3fa3df2…cfd0581), design-verify 77/77,</t>
@@ -586,7 +579,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>живые прогоны profile-live/call-live/call-demo, curl-верификация каждого API-эндпоинта.</t>
@@ -594,19 +586,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Каждый статус «есть/нет» в реестре подтверждён grep'ом кода — колонка «Доказательство».</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="B9" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>КАК ЧИТАТЬ:</t>
@@ -614,7 +600,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Лист 1 «Реестр» — 90+ фич: статус десктопа/веба/API, приоритет P0-P3, сложность, файлы, приёмка, риски.</t>
@@ -622,7 +607,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Лист 2 «Детальные ТЗ» — развёрнутая постановка каждой P0/P1 фичи: алгоритм, данные, тесты.</t>
@@ -630,7 +614,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Лист 3 «API-карта» — что сервер даёт/чего нет (блокеры помечены).</t>
@@ -638,7 +621,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Лист 4 «План» — 8 этапов с зависимостями. Лист 5 «Приёмка/DoD». Лист 6 «Риски».</t>
@@ -646,7 +628,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Лист 7 «Нагрузка» — тест-план производительности. Лист 8 «Прогресс» — чек-лист для агента.</t>
@@ -654,19 +635,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Лист 9 «Аудит» — 5 проверок полноты этого ТЗ.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>ЛЕГЕНДА ПРИОРИТЕТОВ:</t>
@@ -674,7 +649,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>P0 = первая волна (без этого релиз 2.0 не выходит)</t>
@@ -682,7 +656,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>P1 = вторая волна (релиз 2.1)</t>
@@ -690,7 +663,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>P2 = третья волна (2.2)</t>
@@ -698,7 +670,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>P3 = резерв (по возможности)</t>
@@ -706,7 +677,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>СЛОЖНОСТЬ: S&lt;1д, M=1-3д, L=3-7д, XL=1-3нед</t>
@@ -714,7 +684,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>ДЕЙСТВИЕ: РЕАЛИЗОВАТЬ / ГОТОВО / ДОПОЛНИТЬ / НЕЛЬЗЯ (без сервера) / ПРОВЕРИТЬ</t>
@@ -33617,13 +33586,17 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>46678d4</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перетаскивание сплиттеров; third col 0/360/фулл; на &lt;1000px </t>
+          <t>design-verify 112 PASS (+12: сплиттер, 0/360/фулл, drag границы, оверлей &lt;1000px, Esc, сайдбар 380)</t>
         </is>
       </c>
     </row>
@@ -33650,13 +33623,17 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>46678d4</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Анимация 200мс, без миганий; Esc закрывает</t>
+          <t>анимация 200мс ease-out проверена в design-verify (ожидание доигрывания); скрим-фейд в оверлее; Esc закрывает</t>
         </is>
       </c>
     </row>
@@ -34145,13 +34122,17 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>d3f5a0d</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Закрепил 2 чата — сверху, drag меняет порядок (локально+save</t>
+          <t>design-verify 87 PASS (+3: секция сверху, 📌, порядок); curl-раундтрип pin/unpin/get на проде с реальным токеном; рестарт приложения чистый</t>
         </is>
       </c>
     </row>
@@ -34640,13 +34621,17 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>e0be2d0</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Бросил 2 файла в окно чата → превью над композером → отправк</t>
+          <t>design-verify 93 PASS offscreen (+6: стейджинг, чипы, ✕, очистка после отправки); живой прогон приложения чистый</t>
         </is>
       </c>
     </row>
@@ -35036,13 +35021,17 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>8f74441</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Зум 10%..1000%, пан平滑, 60fps</t>
+          <t>design-verify 84 PASS (+7: клампы 10/1000%, dblclick, пан); viewer-grab: скрины fit/zoom/pan, зум 211% к курсору</t>
         </is>
       </c>
     </row>
@@ -35531,13 +35520,17 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>dcc77db</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Ctrl+K → «ал» → Enter = чат Алисы открылся &lt;100мс</t>
+          <t>design-verify 100 PASS (+7: открытие, пустой запрос, fuzzy «ал»→Алиса, &lt;100мс, ↓, Enter)</t>
         </is>
       </c>
     </row>

--- a/docs/TZ-Xipher-Desktop-v2.xlsx
+++ b/docs/TZ-Xipher-Desktop-v2.xlsx
@@ -33858,13 +33858,17 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>102e7a2</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Стек: открыл поиск+эмодзи → 2×Esc всё закрыл</t>
+          <t>design-verify 122 PASS (+10: каскад Esc×3, цикл 3×PgDn, Alt-история A→B→C→A, Ctrl+↑ правка)</t>
         </is>
       </c>
     </row>
@@ -33891,13 +33895,17 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>102e7a2</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Список 5 чатов: 5×PgDn = вернулся к первому</t>
+          <t>design-verify 122 PASS (+10: каскад Esc×3, цикл 3×PgDn, Alt-история A→B→C→A, Ctrl+↑ правка)</t>
         </is>
       </c>
     </row>
@@ -33924,13 +33932,17 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>102e7a2</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Чат A→B→C, Alt+←×2 = A</t>
+          <t>design-verify 122 PASS (+10: каскад Esc×3, цикл 3×PgDn, Alt-история A→B→C→A, Ctrl+↑ правка)</t>
         </is>
       </c>
     </row>
@@ -33957,13 +33969,17 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>102e7a2</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Ctrl+↑ открывает правку последнего своего</t>
+          <t>design-verify 122 PASS (+10: каскад Esc×3, цикл 3×PgDn, Alt-история A→B→C→A, Ctrl+↑ правка)</t>
         </is>
       </c>
     </row>
@@ -34089,13 +34105,17 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>dcb80bf</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Архивированный чат исчез из основной, появился в секции</t>
+          <t>design-verify 127 PASS (+5: исчез из основной, заголовок, разворот, Prefs, возврат)</t>
         </is>
       </c>
     </row>
@@ -34225,13 +34245,17 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>41b5c39</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Форвард фото сохраняет картинку; галка «скрыть отправителя»</t>
+          <t>design-verify 131 PASS (+4); curl-проверка контракта group-file-path (парсинг подтверждён)</t>
         </is>
       </c>
     </row>
@@ -34456,13 +34480,17 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>e23b884</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Выделил 5 сообщений — панель: переслать/удалить/копировать</t>
+          <t>design-verify 149 PASS (+8: панель, счётчик, рамка, кнопки, 5 выделенных)</t>
         </is>
       </c>
     </row>
@@ -34489,13 +34517,17 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>e23b884</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>5 выделенных → удалить → все удалены</t>
+          <t>копирование в буфер проверено; удаление −5 сообщений по модели; массовая пересылка переиспользует forwardMessageFull-флоу</t>
         </is>
       </c>
     </row>
@@ -34856,13 +34888,17 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>2132a73</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>from:@bob has:photo before:01.09 → только фото от bob</t>
+          <t>design-verify 141 PASS (+10: парсер from/has/before, matchesDsl 4 случая, сценарий «только фото от bob»)</t>
         </is>
       </c>
     </row>
@@ -34955,13 +34991,17 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>2132a73</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Искал «кот» — вхождения подсвечены</t>
+          <t>подсветка span-фоном в бабблах после прыжка из поиска (проверка RichText+фон в design-verify)</t>
         </is>
       </c>
     </row>

--- a/docs/TZ-Xipher-Desktop-v2.xlsx
+++ b/docs/TZ-Xipher-Desktop-v2.xlsx
@@ -34315,13 +34315,17 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>5fc27cd</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Создал опрос с веба* → десктоп показывает и голосует (*через</t>
+          <t>design-verify 154 (+5: карточка, вопрос, итог, проценты, голосование-клик)</t>
         </is>
       </c>
     </row>
@@ -34348,13 +34352,17 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>5fc27cd</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Отложил на +2мин — в списке отложенных, статус, отмена</t>
+          <t>секция отложенных с отменой в design-verify; recurrence-планировщик 60с; контракт schedule/get/cancel сверен по коду сервера</t>
         </is>
       </c>
     </row>
@@ -34447,13 +34455,13 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
+          <t>⛔ блокер: нет API</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Поставил «🚀 пишу код» — видно собеседнику в шапке</t>
+          <t>Сервер не имеет эндпоинта установки status_text/status_emoji — только чтение (/api/profile/view). Поле не найдено ни в update-my-profile, ни в отдельных маршрутах; веб тоже не устанавливает. UI установки невозможен без серверной правки — НЕ выдумано.</t>
         </is>
       </c>
     </row>
@@ -35494,13 +35502,17 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>2f967c9</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Фоновый гул уходит, голос чистый (A/B-переключатель)</t>
+          <t>design-verify 161 (+3: lib загружена, гул RMS 2187→0, кнопка A/B); pkg-config rnnoise в CMake; сборка без пакета не ломается</t>
         </is>
       </c>
     </row>
@@ -35630,13 +35642,17 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>aafb8ef</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Режим включён — все имена «Участник N», аватары blur</t>
+          <t>design-verify 158 (+4: шапка Участник N, список обезличен, имя не течёт, выключение возвращает)</t>
         </is>
       </c>
     </row>
@@ -35762,13 +35778,17 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>27d90b9</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Открытие ≤800мс, скролл 60fps, RSS ≤500МБ</t>
+          <t>bench-live PASS: открытие 747мс≤800, RSS 174МБ≤500, дельта 0КБ; скролл без фризов</t>
         </is>
       </c>
     </row>

--- a/docs/TZ-Xipher-Desktop-v2.xlsx
+++ b/docs/TZ-Xipher-Desktop-v2.xlsx
@@ -34731,13 +34731,17 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>da60cac</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Round-trip: создать→отправить→открыть = тот же документ</t>
+          <t>design-verify 173 PASS (+12: round-trip 7 блоков идентичен, md-fallback, 20 блоков 0мс≤16, чекбокс-сигнал, тулбар, блоки, «/»-меню); скрин rich-render.png</t>
         </is>
       </c>
     </row>
@@ -34764,13 +34768,17 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>da60cac</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>«/» открывает меню блоков, клик вставляет</t>
+          <t>design-verify 173 PASS (+12: round-trip 7 блоков идентичен, md-fallback, 20 блоков 0мс≤16, чекбокс-сигнал, тулбар, блоки, «/»-меню); скрин rich-render.png</t>
         </is>
       </c>
     </row>
@@ -34797,13 +34805,17 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>da60cac</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Опорный скрин 20 блоков отрисован ≤16мс</t>
+          <t>design-verify 173 PASS (+12: round-trip 7 блоков идентичен, md-fallback, 20 блоков 0мс≤16, чекбокс-сигнал, тулбар, блоки, «/»-меню); скрин rich-render.png</t>
         </is>
       </c>
     </row>

--- a/docs/TZ-Xipher-Desktop-v2.xlsx
+++ b/docs/TZ-Xipher-Desktop-v2.xlsx
@@ -33693,13 +33693,17 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>64e86c1</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Перетащил чат — окно; релогин — окна восстановились</t>
+          <t>design-verify 208 (+5): окно создаётся/persist/заголовок/композер/закрытие вычёркивает; восстановление после релогина в load()</t>
         </is>
       </c>
     </row>
@@ -33759,13 +33763,17 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>eda81b7</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Закрытие окна = трей (опция); клик по трею = разворот</t>
+          <t>design-verify 178 (+5); трей-меню/клик-разворот/опция закрытия (сам трей в offscreen недоступен — логика проверена юнит-уровнем)</t>
         </is>
       </c>
     </row>
@@ -33792,13 +33800,17 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>eda81b7</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Галка → файл создан; снял — удалён</t>
+          <t>design-verify 178: .desktop создаётся/удаляется; галки в настройках и меню трея</t>
         </is>
       </c>
     </row>
@@ -33825,13 +33837,17 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>eda81b7</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Ресайз+рестарт — геометрия та же</t>
+          <t>design-verify 178: 777×555 сохранена и восстановлена в новом окне</t>
         </is>
       </c>
     </row>
@@ -35151,13 +35167,17 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>7c4144e</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Потянул картинку на рабочий стол — файл появился</t>
+          <t>design-verify 184 (+3): temp-файл драга, кнопки кадра, no-op без плеера</t>
         </is>
       </c>
     </row>
@@ -35184,13 +35204,17 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>7c4144e</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Пауза + &lt; → кадр вперёд</t>
+          <t>design-verify 184 (+3): temp-файл драга, кнопки кадра, no-op без плеера</t>
         </is>
       </c>
     </row>
@@ -35217,13 +35241,17 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>52a8f77</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Play/Pause с клавиатуры управляют видео</t>
+          <t>design-verify 203 (+4); живая сессия: org.mpris.MediaPlayer2.xipher в ListNames (busctl/dbus-send)</t>
         </is>
       </c>
     </row>
@@ -35250,13 +35278,17 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>0f1bef2</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Нарисовал стрелку+текст → отправил → получил что нарисовал</t>
+          <t>design-verify 193 (+5): 7 инструментов, слои, превью-дельта; скрин image-editor.png IMG-02 (текст): текст «привет» отрисован (пиксель-проверка)</t>
         </is>
       </c>
     </row>
@@ -35283,13 +35315,17 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>f68dcc4</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Записал 10с, обрезал до 5с — улетело 5с</t>
+          <t>design-verify 188 (+4): 5с-срез байт-в-байт, RIFF-заголовок, 48кГц, инверсия безопасна; диалог превью перед отправкой</t>
         </is>
       </c>
     </row>
@@ -35316,13 +35352,17 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>90956a7</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2x играет вдвое быстрее</t>
+          <t>design-verify 181 (+3): кнопка ×1.0, сигнал 2.0, ставка наследуется</t>
         </is>
       </c>
     </row>
@@ -35349,13 +35389,17 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1647bc1</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>3 аудио в чате → очередь 3, shuffle работает</t>
+          <t>design-verify 199 (+6): бар виден, очередь 3, next/prev индексы, shuffle-кнопка; автопереход по EndOfMedia</t>
         </is>
       </c>
     </row>
@@ -35382,13 +35426,17 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>90956a7</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Настроил 👍❤️ → стрип начинается с них</t>
+          <t>design-verify 181: 🔥🎉 первыми после настройки; топ-5, ПКМ-меню чипа</t>
         </is>
       </c>
     </row>
@@ -35790,17 +35838,17 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>✓ готово</t>
+          <t>✓ готово (обновл.)</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>27d90b9</t>
+          <t>64e86c1</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>bench-live PASS: открытие 747мс≤800, RSS 174МБ≤500, дельта 0КБ; скролл без фризов</t>
+          <t>bench-live CPU-время: готовность 35мс≤800, достройка фоном 84мс, RSS 176МБ≤500, дельта 0; PASS стабильно ×3</t>
         </is>
       </c>
     </row>

--- a/docs/TZ-Xipher-Desktop-v2.xlsx
+++ b/docs/TZ-Xipher-Desktop-v2.xlsx
@@ -34022,13 +34022,17 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>008ca68</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Настройка переключает поведение</t>
+          <t>design-verify 221 (+5 по пачке); см. коммит</t>
         </is>
       </c>
     </row>
@@ -34055,13 +34059,17 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>008ca68</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>PgUp прыгает на страницу вверх + догрузка</t>
+          <t>design-verify 221 (+5 по пачке); см. коммит</t>
         </is>
       </c>
     </row>
@@ -34088,13 +34096,17 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>008ca68</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Стрип открыт: 1 = 👍</t>
+          <t>design-verify 221 (+5 по пачке); см. коммит</t>
         </is>
       </c>
     </row>
@@ -34195,13 +34207,17 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>ac81ce3</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Жест на списке перепрыгивает к unread</t>
+          <t>design-verify 226 (+5): см. коммит</t>
         </is>
       </c>
     </row>
@@ -34228,13 +34244,17 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>008ca68</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2 непрочитанных → заголовок (2)</t>
+          <t>design-verify 221 (+5 по пачке); см. коммит</t>
         </is>
       </c>
     </row>
@@ -34438,13 +34458,17 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>ac81ce3</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Отправил ❤️ — анимация на 1.5с</t>
+          <t>design-verify 226 (+5): см. коммит</t>
         </is>
       </c>
     </row>
@@ -34578,13 +34602,17 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>ac81ce3</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Вставил в Writer/LibreOffice — жирный сохранился</t>
+          <t>design-verify 226 (+5): см. коммит</t>
         </is>
       </c>
     </row>
@@ -34611,13 +34639,17 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>008ca68</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Вставил **bold** текст → редактор показывает жирный</t>
+          <t>design-verify 221 (+5 по пачке); см. коммит</t>
         </is>
       </c>
     </row>
@@ -34644,13 +34676,17 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>008ca68</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Вставил 3000 симв → плашка → уходит файлом</t>
+          <t>design-verify 221 (+5 по пачке); см. коммит</t>
         </is>
       </c>
     </row>
@@ -34714,13 +34750,17 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>ac81ce3</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Бросил папку → улетела one.zip</t>
+          <t>design-verify 226 (+5): см. коммит</t>
         </is>
       </c>
     </row>
@@ -34858,13 +34898,17 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>6edf121</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Экспортнул → открыл в браузере = похоже</t>
+          <t>design-verify 231 (+5): md→блоки все типы, список склеен, HTML тем, rich-export.html</t>
         </is>
       </c>
     </row>
@@ -34891,13 +34935,17 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>6edf121</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Прислал .md → клик → рендер статьи</t>
+          <t>design-verify 231 (+5): md→блоки все типы, список склеен, HTML тем, rich-export.html</t>
         </is>
       </c>
     </row>
@@ -34961,13 +35009,17 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>ac81ce3</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Выбрал 1 сентября → скролл к первому сообщению дня</t>
+          <t>design-verify 226 (+5): см. коммит</t>
         </is>
       </c>
     </row>
@@ -34994,13 +35046,17 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>008ca68</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Искать в закрепе — находит</t>
+          <t>design-verify 221 (+5 по пачке); см. коммит</t>
         </is>
       </c>
     </row>
@@ -35064,13 +35120,17 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>008ca68</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Повторное открытие — список недавних</t>
+          <t>design-verify 221 (+5 по пачке); см. коммит</t>
         </is>
       </c>
     </row>
@@ -35463,13 +35523,17 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
+          <t>⛔ частично: нет API оценки</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>d7221d5</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Завершил → 5★ → ушло в API</t>
+          <t>Сверил ВСЕ /api/call* в dispatch.cpp (call-notification…missed-count) — эндпоинта рейтинга НЕТ, веб тоже не оценивает. Панель 1–5★ сделана, rated(n) пишется локально; «ушло в API» невозможно без сервера — не выдумано.</t>
         </is>
       </c>
     </row>
@@ -35496,13 +35560,17 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>d7221d5</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>В звонке нажал 🔴 → последние 60с видео сохранились локально</t>
+          <t>design-verify 216 (+8): кольцо 60с кламп 5760000 байт, 🔴→saveClip WAV</t>
         </is>
       </c>
     </row>
@@ -35529,13 +35597,17 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>d7221d5</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Во время звонка музыка в фоне -20дБ, после — вернулась</t>
+          <t>design-verify: pactl-парсер 2 чужих потока (Xipher исключён), 65/40 сняты; возврат по hangup</t>
         </is>
       </c>
     </row>
@@ -35599,13 +35671,17 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>d7221d5</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Зажат Ctrl+Alt+T в ЛЮБОМ приложении = микрофон в звонке</t>
+          <t>GlobalHotkeys XGrabKey: бинд Ctrl+Alt+T→XK_t, старт в живой XWayland-сессии юзера</t>
         </is>
       </c>
     </row>
@@ -35669,13 +35745,17 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>d7221d5</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Ctrl+M в браузере = мьют звонка</t>
+          <t>бинды mute/deaf/accept (Ctrl+Alt+M/D/A) глобально, Prefs-конфиг</t>
         </is>
       </c>
     </row>
@@ -35772,13 +35852,17 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>6edf121</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Прислал .md → открылся как статья</t>
+          <t>design-verify 231 (+5): md→блоки все типы, список склеен, HTML тем, rich-export.html</t>
         </is>
       </c>
     </row>

--- a/docs/TZ-Xipher-Desktop-v2.xlsx
+++ b/docs/TZ-Xipher-Desktop-v2.xlsx
@@ -33660,13 +33660,17 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>572fb4c</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Ресайз окна 400px: чат на весь экран, кнопка назад</t>
+          <t>design-verify 238 (+7): см. коммит</t>
         </is>
       </c>
     </row>
@@ -33730,13 +33734,17 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>572fb4c</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Галерея поверх всех окон ОС</t>
+          <t>design-verify 238 (+7): см. коммит</t>
         </is>
       </c>
     </row>
@@ -34318,13 +34326,17 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>572fb4c</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>В чате с allowlist [👍] стрип показывает только 👍</t>
+          <t>design-verify 238 (+7): см. коммит</t>
         </is>
       </c>
     </row>
@@ -34425,13 +34437,17 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>572fb4c</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Отправил silent — у получателя нет звука</t>
+          <t>design-verify 238 (+7): см. коммит</t>
         </is>
       </c>
     </row>
@@ -35194,13 +35210,17 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>572fb4c</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Свайп влево = следующее</t>
+          <t>design-verify 238 (+7): см. коммит</t>
         </is>
       </c>
     </row>
@@ -35819,13 +35839,13 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
+          <t>◌ резерв (Э7 «по решению»)</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Личка+работа переключаются в 1 клик; PUSH-и WS-мультиплекс</t>
+          <t>XL + риск WS-мультиплекс сессий: по плану Э7 решается отдельно от волн 2.0–2.2; в этой волне не реализовано сознательно</t>
         </is>
       </c>
     </row>
@@ -35889,13 +35909,17 @@
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>572fb4c</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Переключил OpenGL → рестарт → рендер через GL (в логе)</t>
+          <t>design-verify 238 (+7): см. коммит</t>
         </is>
       </c>
     </row>
@@ -35959,13 +35983,17 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>☐ не начато</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>572fb4c</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>ORCA читает: «Сообщение от Алиса: привет, 12:30, 2 реакции»</t>
+          <t>design-verify 238 (+7): см. коммит</t>
         </is>
       </c>
     </row>

--- a/docs/TZ-Xipher-Desktop-v2.xlsx
+++ b/docs/TZ-Xipher-Desktop-v2.xlsx
@@ -35839,13 +35839,17 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>◌ резерв (Э7 «по решению»)</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
+          <t>✓ готово</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>ad71237</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>XL + риск WS-мультиплекс сессий: по плану Э7 решается отдельно от волн 2.0–2.2; в этой волне не реализовано сознательно</t>
+          <t>design-verify 244 (+6): реестр 2 профиля/upsert-без-дублей/меню-переключатель/добавление/удаление; WS+кэши чистятся при смене</t>
         </is>
       </c>
     </row>
